--- a/运气工程/运气工程-03-SlotsRTP计算规则-基础篇.xlsx
+++ b/运气工程/运气工程-03-SlotsRTP计算规则-基础篇.xlsx
@@ -7368,6 +7368,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F72" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8858,6 +8861,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M77" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10387,6 +10393,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V47" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10925,6 +10934,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L41" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11392,6 +11404,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J46" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11914,5 +11929,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K44" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/运气工程/运气工程-03-SlotsRTP计算规则-基础篇.xlsx
+++ b/运气工程/运气工程-03-SlotsRTP计算规则-基础篇.xlsx
@@ -14,7 +14,7 @@
     <sheet name="满线Ways" sheetId="5" r:id="rId5"/>
     <sheet name="易错点-窗口环绕" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="198">
   <si>
     <r>
       <rPr>
@@ -6524,7 +6524,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -6575,6 +6575,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -7295,18 +7306,18 @@
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="29" t="s">
-        <v>33</v>
+      <c r="A39" s="31">
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="29" t="s">
-        <v>34</v>
+      <c r="A40" s="31">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="29" t="s">
-        <v>35</v>
+      <c r="A41" s="31">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -7386,8 +7397,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="22" t="s">
-        <v>46</v>
+      <c r="A1" s="32">
+        <v>3</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -7681,8 +7692,8 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>58</v>
+      <c r="B13" s="33">
+        <v>10</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>57</v>
@@ -7707,8 +7718,8 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>58</v>
+      <c r="B14" s="33">
+        <v>10</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>57</v>
@@ -7733,8 +7744,8 @@
       <c r="A15">
         <v>11</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>58</v>
+      <c r="B15" s="33">
+        <v>10</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>57</v>
@@ -7759,20 +7770,20 @@
       <c r="A16">
         <v>12</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>58</v>
+      <c r="B16" s="33">
+        <v>10</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>58</v>
+      <c r="D16" s="33">
+        <v>10</v>
+      </c>
+      <c r="E16" s="33">
+        <v>10</v>
+      </c>
+      <c r="F16" s="33">
+        <v>10</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>1</v>
@@ -7785,20 +7796,20 @@
       <c r="A17">
         <v>13</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>58</v>
+      <c r="B17" s="33">
+        <v>10</v>
+      </c>
+      <c r="C17" s="33">
+        <v>10</v>
+      </c>
+      <c r="D17" s="33">
+        <v>10</v>
+      </c>
+      <c r="E17" s="33">
+        <v>10</v>
+      </c>
+      <c r="F17" s="33">
+        <v>10</v>
       </c>
       <c r="G17" s="19" t="s">
         <v>1</v>
@@ -7811,20 +7822,20 @@
       <c r="A18">
         <v>14</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>58</v>
+      <c r="B18" s="33">
+        <v>9</v>
+      </c>
+      <c r="C18" s="33">
+        <v>10</v>
+      </c>
+      <c r="D18" s="33">
+        <v>10</v>
+      </c>
+      <c r="E18" s="33">
+        <v>10</v>
+      </c>
+      <c r="F18" s="33">
+        <v>10</v>
       </c>
       <c r="G18" s="19" t="s">
         <v>1</v>
@@ -7837,20 +7848,20 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>58</v>
+      <c r="B19" s="33">
+        <v>9</v>
+      </c>
+      <c r="C19" s="33">
+        <v>10</v>
+      </c>
+      <c r="D19" s="33">
+        <v>10</v>
+      </c>
+      <c r="E19" s="33">
+        <v>10</v>
+      </c>
+      <c r="F19" s="33">
+        <v>10</v>
       </c>
       <c r="G19" s="19" t="s">
         <v>1</v>
@@ -7863,20 +7874,20 @@
       <c r="A20">
         <v>16</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>59</v>
+      <c r="B20" s="33">
+        <v>9</v>
+      </c>
+      <c r="C20" s="33">
+        <v>9</v>
+      </c>
+      <c r="D20" s="33">
+        <v>9</v>
+      </c>
+      <c r="E20" s="33">
+        <v>9</v>
+      </c>
+      <c r="F20" s="33">
+        <v>9</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>1</v>
@@ -7889,20 +7900,20 @@
       <c r="A21">
         <v>17</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>59</v>
+      <c r="B21" s="33">
+        <v>9</v>
+      </c>
+      <c r="C21" s="33">
+        <v>9</v>
+      </c>
+      <c r="D21" s="33">
+        <v>9</v>
+      </c>
+      <c r="E21" s="33">
+        <v>9</v>
+      </c>
+      <c r="F21" s="33">
+        <v>9</v>
       </c>
       <c r="G21" s="19" t="s">
         <v>1</v>
@@ -7915,20 +7926,20 @@
       <c r="A22">
         <v>18</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>59</v>
+      <c r="B22" s="33">
+        <v>9</v>
+      </c>
+      <c r="C22" s="33">
+        <v>9</v>
+      </c>
+      <c r="D22" s="33">
+        <v>9</v>
+      </c>
+      <c r="E22" s="33">
+        <v>9</v>
+      </c>
+      <c r="F22" s="33">
+        <v>9</v>
       </c>
       <c r="G22" s="19" t="s">
         <v>1</v>
@@ -7941,20 +7952,20 @@
       <c r="A23">
         <v>19</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>59</v>
+      <c r="B23" s="33">
+        <v>9</v>
+      </c>
+      <c r="C23" s="33">
+        <v>9</v>
+      </c>
+      <c r="D23" s="33">
+        <v>9</v>
+      </c>
+      <c r="E23" s="33">
+        <v>9</v>
+      </c>
+      <c r="F23" s="33">
+        <v>9</v>
       </c>
       <c r="G23" s="19" t="s">
         <v>1</v>
@@ -8255,8 +8266,8 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="5" t="s">
-        <v>58</v>
+      <c r="A34" s="34">
+        <v>10</v>
       </c>
       <c r="B34" s="6">
         <f t="shared" si="0"/>
@@ -8286,8 +8297,8 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="5" t="s">
-        <v>59</v>
+      <c r="A35" s="34">
+        <v>9</v>
       </c>
       <c r="B35" s="6">
         <f t="shared" si="0"/>
@@ -8424,14 +8435,14 @@
       <c r="A40" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>70</v>
+      <c r="B40" s="35">
+        <v>3</v>
+      </c>
+      <c r="C40" s="35">
+        <v>4</v>
+      </c>
+      <c r="D40" s="35">
+        <v>5</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>1</v>
@@ -8525,8 +8536,8 @@
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="5" t="s">
-        <v>58</v>
+      <c r="A44" s="34">
+        <v>10</v>
       </c>
       <c r="B44" s="10">
         <v>5</v>
@@ -8551,8 +8562,8 @@
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="5" t="s">
-        <v>59</v>
+      <c r="A45" s="34">
+        <v>9</v>
       </c>
       <c r="B45" s="10">
         <v>5</v>
@@ -9042,14 +9053,14 @@
       <c r="I4" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>99</v>
+      <c r="J4" s="35">
+        <v>5</v>
+      </c>
+      <c r="K4" s="35">
+        <v>4</v>
+      </c>
+      <c r="L4" s="35">
+        <v>3</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>100</v>
@@ -9272,8 +9283,8 @@
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="5" t="s">
-        <v>58</v>
+      <c r="A8" s="34">
+        <v>10</v>
       </c>
       <c r="B8" s="6">
         <f>滚轴与赔付!B34+滚轴与赔付!B$30</f>
@@ -9340,8 +9351,8 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="5" t="s">
-        <v>59</v>
+      <c r="A9" s="34">
+        <v>9</v>
       </c>
       <c r="B9" s="6">
         <f>滚轴与赔付!B35+滚轴与赔付!B$30</f>
@@ -11020,8 +11031,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="5" t="s">
-        <v>146</v>
+      <c r="A5" s="34">
+        <v>3</v>
       </c>
       <c r="B5" s="10">
         <v>3</v>
@@ -11038,8 +11049,8 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="5" t="s">
-        <v>148</v>
+      <c r="A6" s="34">
+        <v>4</v>
       </c>
       <c r="B6" s="10">
         <v>4</v>
@@ -11056,8 +11067,8 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="5" t="s">
-        <v>149</v>
+      <c r="A7" s="34">
+        <v>5</v>
       </c>
       <c r="B7" s="10">
         <v>5</v>
@@ -11074,8 +11085,8 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="5" t="s">
-        <v>150</v>
+      <c r="A8" s="34">
+        <v>3</v>
       </c>
       <c r="B8" s="10">
         <v>3</v>
@@ -11092,8 +11103,8 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
-        <v>151</v>
+      <c r="A9" s="34">
+        <v>4</v>
       </c>
       <c r="B9" s="10">
         <v>4</v>
@@ -11179,8 +11190,8 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
-        <v>155</v>
+      <c r="A14" s="34">
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
@@ -11675,8 +11686,8 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>58</v>
+      <c r="A13" s="34">
+        <v>10</v>
       </c>
       <c r="B13" s="6">
         <f>COUNTIF(滚轴与赔付!$B$5:$B$24,$A13)</f>
@@ -11699,8 +11710,8 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>59</v>
+      <c r="A14" s="34">
+        <v>9</v>
       </c>
       <c r="B14" s="6">
         <f>COUNTIF(滚轴与赔付!$B$5:$B$24,$A14)</f>

--- a/运气工程/运气工程-03-SlotsRTP计算规则-基础篇.xlsx
+++ b/运气工程/运气工程-03-SlotsRTP计算规则-基础篇.xlsx
@@ -5813,13 +5813,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
+    <numFmt numFmtId="178" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -6524,7 +6525,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -6587,6 +6588,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -9138,7 +9141,7 @@
         <f>VLOOKUP($A5,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="36">
         <f>(J5*M5+K5*N5+L5*O5)/滚轴与赔付!$H$25</f>
         <v>0.0256</v>
       </c>
@@ -9206,7 +9209,7 @@
         <f>VLOOKUP($A6,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="36">
         <f>(J6*M6+K6*N6+L6*O6)/滚轴与赔付!$H$25</f>
         <v>0.072</v>
       </c>
@@ -9274,7 +9277,7 @@
         <f>VLOOKUP($A7,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="36">
         <f>(J7*M7+K7*N7+L7*O7)/滚轴与赔付!$H$25</f>
         <v>0.1828125</v>
       </c>
@@ -9342,7 +9345,7 @@
         <f>VLOOKUP($A8,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="36">
         <f>(J8*M8+K8*N8+L8*O8)/滚轴与赔付!$H$25</f>
         <v>0.15234375</v>
       </c>
@@ -9410,7 +9413,7 @@
         <f>VLOOKUP($A9,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="36">
         <f>(J9*M9+K9*N9+L9*O9)/滚轴与赔付!$H$25</f>
         <v>0.1640625</v>
       </c>
@@ -9467,7 +9470,7 @@
       <c r="O10" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="37">
         <f>SUM(P5:P9)</f>
         <v>0.59681875</v>
       </c>
@@ -9591,7 +9594,7 @@
       <c r="C13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="36">
         <f>(J10+K10+L10)/滚轴与赔付!$H$25</f>
         <v>0.05425</v>
       </c>
@@ -9645,7 +9648,7 @@
       <c r="C14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="36">
         <f>P10</f>
         <v>0.59681875</v>
       </c>
@@ -9979,7 +9982,7 @@
         <f>滚轴与赔付!F50</f>
         <v>1</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="36">
         <f>$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -9987,11 +9990,11 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="36">
         <f>G20*H20</f>
         <v>0.59681875</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="37">
         <f>I20/H20</f>
         <v>0.59681875</v>
       </c>
@@ -10041,7 +10044,7 @@
         <f>滚轴与赔付!F51</f>
         <v>2</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="36">
         <f>$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10049,11 +10052,11 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="36">
         <f>G21*H21</f>
         <v>0.59681875</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="37">
         <f>I21/H21</f>
         <v>0.59681875</v>
       </c>
@@ -10103,7 +10106,7 @@
         <f>滚轴与赔付!F52</f>
         <v>3</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="36">
         <f>$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10111,11 +10114,11 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="36">
         <f>G22*H22</f>
         <v>0.59681875</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="37">
         <f>I22/H22</f>
         <v>0.59681875</v>
       </c>
@@ -10165,7 +10168,7 @@
         <f>滚轴与赔付!F53</f>
         <v>1</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="36">
         <f>$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10173,11 +10176,11 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="36">
         <f>G23*H23</f>
         <v>0.59681875</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="37">
         <f>I23/H23</f>
         <v>0.59681875</v>
       </c>
@@ -10227,7 +10230,7 @@
         <f>滚轴与赔付!F54</f>
         <v>3</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="36">
         <f>$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10235,11 +10238,11 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="36">
         <f>G24*H24</f>
         <v>0.59681875</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="37">
         <f>I24/H24</f>
         <v>0.59681875</v>
       </c>
@@ -10735,11 +10738,11 @@
         <f>A14*$B$6</f>
         <v>1</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="36">
         <f>线型与RTP!$D$13</f>
         <v>0.05425</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="36">
         <f>1-(1-C14)^A14</f>
         <v>0.05425</v>
       </c>
@@ -10747,7 +10750,7 @@
         <f>B14*线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="37">
         <f>线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10764,11 +10767,11 @@
         <f>A15*$B$6</f>
         <v>2</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="36">
         <f>线型与RTP!$D$13</f>
         <v>0.05425</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="36">
         <f>1-(1-C15)^A15</f>
         <v>0.1055569375</v>
       </c>
@@ -10776,7 +10779,7 @@
         <f>B15*线型与RTP!$P$10</f>
         <v>1.1936375</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="37">
         <f>线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10793,11 +10796,11 @@
         <f>A16*$B$6</f>
         <v>3</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="36">
         <f>线型与RTP!$D$13</f>
         <v>0.05425</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="36">
         <f>1-(1-C16)^A16</f>
         <v>0.154080473640625</v>
       </c>
@@ -10805,7 +10808,7 @@
         <f>B16*线型与RTP!$P$10</f>
         <v>1.79045625</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="37">
         <f>线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10822,11 +10825,11 @@
         <f>A17*$B$6</f>
         <v>4</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="36">
         <f>线型与RTP!$D$13</f>
         <v>0.05425</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="36">
         <f>1-(1-C17)^A17</f>
         <v>0.199971607945621</v>
       </c>
@@ -10834,7 +10837,7 @@
         <f>B17*线型与RTP!$P$10</f>
         <v>2.387275</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="37">
         <f>线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -10851,11 +10854,11 @@
         <f>A18*$B$6</f>
         <v>5</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="36">
         <f>线型与RTP!$D$13</f>
         <v>0.05425</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="36">
         <f>1-(1-C18)^A18</f>
         <v>0.243373148214571</v>
       </c>
@@ -10863,7 +10866,7 @@
         <f>B18*线型与RTP!$P$10</f>
         <v>2.98409375</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="37">
         <f>线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -11837,7 +11840,7 @@
       <c r="A20" t="s">
         <v>194</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="36">
         <f>线型与RTP!$P$10</f>
         <v>0.59681875</v>
       </c>
@@ -11858,7 +11861,7 @@
       <c r="A21" t="s">
         <v>195</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="36">
         <f>0.3140109375</f>
         <v>0.3140109375</v>
       </c>
@@ -11879,7 +11882,7 @@
       <c r="A22" t="s">
         <v>196</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="36">
         <f>B20-B21</f>
         <v>0.2828078125</v>
       </c>
